--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/328479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/342133</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,6153 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/342133</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135849960</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96486</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500101</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7003128</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849960</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135849961</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96486</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500108</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7003086</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849961</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135849962</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96486</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7003128</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849962</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135850021</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500042</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7003097</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135850022</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500034</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7003063</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135849908</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499900</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7003040</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På en gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849908</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135849879</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>500051</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7003122</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849879</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135849846</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>500028</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7003043</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849846</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135849847</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499895</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7003040</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, enstaka på en gran.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849847</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135849848</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499850</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7003017</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849848</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135849849</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499846</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7003017</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849849</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135849871</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>500027</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7003080</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849871</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135849872</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>499957</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7003085</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849872</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135849868</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>500049</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7003051</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849868</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135849938</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>500061</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7003131</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849938</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135849939</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>500121</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7003069</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849939</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135849940</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>500102</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7003063</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849940</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135849941</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>500056</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7003057</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849941</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135849942</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>500008</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7003091</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849942</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135849943</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>500012</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7003122</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849943</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135849945</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>500034</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7003139</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849945</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135849946</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7003116</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849946</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135849947</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499954</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7003072</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849947</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135849948</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99612</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>499965</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7003087</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849948</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135850036</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>499997</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7003107</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850036</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135849924</v>
+      </c>
+      <c r="B29" t="n">
+        <v>108362</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>500117</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7003169</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849924</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135849925</v>
+      </c>
+      <c r="B30" t="n">
+        <v>108362</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>500067</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7003124</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849925</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135849926</v>
+      </c>
+      <c r="B31" t="n">
+        <v>108362</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>500128</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7003069</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849926</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135849927</v>
+      </c>
+      <c r="B32" t="n">
+        <v>108362</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>500012</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7003082</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849927</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135849928</v>
+      </c>
+      <c r="B33" t="n">
+        <v>108362</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7003122</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849928</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135849929</v>
+      </c>
+      <c r="B34" t="n">
+        <v>108362</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>499925</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7003078</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849929</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135849912</v>
+      </c>
+      <c r="B35" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>500036</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7003072</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849912</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135849986</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>500101</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7003147</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849986</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135849987</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>500113</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7003091</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849987</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135849988</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>500025</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7003030</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849988</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135849865</v>
+      </c>
+      <c r="B39" t="n">
+        <v>110012</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>500092</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7003061</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849865</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135849866</v>
+      </c>
+      <c r="B40" t="n">
+        <v>110012</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>500055</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7003061</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849866</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135849888</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>500042</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849888</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135849890</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>500078</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849890</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135849891</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>499954</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7003071</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849891</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135849999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>500192</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7003171</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849999</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135850000</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>500105</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7003131</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135850001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>500070</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7003120</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850001</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135850002</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>500005</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7003116</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850002</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135850003</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500039</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850003</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135850005</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>499962</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7003092</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850005</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135850006</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>499967</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7003113</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850006</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135849874</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102020</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500036</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7003135</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849874</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135849904</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101373</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849904</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135849905</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101373</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7003121</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849905</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849906</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101373</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500014</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003143</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849906</t>
         </is>
       </c>
     </row>
@@ -904,6 +7051,57 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102020</v>
+        <v>102022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1495,52 +1495,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849908</v>
+        <v>135849879</v>
       </c>
       <c r="B9" t="n">
-        <v>80556</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499900</v>
+        <v>500051</v>
       </c>
       <c r="R9" t="n">
-        <v>7003040</v>
+        <v>7003122</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,24 +1588,18 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1609,33 +1616,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849908</t>
+          <t>https://artportalen.se/Sighting/135849879</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849879</v>
+        <v>135849846</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1643,20 +1650,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1670,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500051</v>
+        <v>500028</v>
       </c>
       <c r="R10" t="n">
-        <v>7003122</v>
+        <v>7003043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,6 +1707,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1720,6 +1724,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1736,13 +1760,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849879</t>
+          <t>https://artportalen.se/Sighting/135849846</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849846</v>
+        <v>135849847</v>
       </c>
       <c r="B11" t="n">
         <v>57980</v>
@@ -1789,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500028</v>
+        <v>499895</v>
       </c>
       <c r="R11" t="n">
-        <v>7003043</v>
+        <v>7003040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1853,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,13 +1904,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849846</t>
+          <t>https://artportalen.se/Sighting/135849847</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849847</v>
+        <v>135849848</v>
       </c>
       <c r="B12" t="n">
         <v>57980</v>
@@ -1933,10 +1957,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499895</v>
+        <v>499850</v>
       </c>
       <c r="R12" t="n">
-        <v>7003040</v>
+        <v>7003017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1973,7 +1997,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,13 +2048,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849847</t>
+          <t>https://artportalen.se/Sighting/135849848</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849848</v>
+        <v>135849849</v>
       </c>
       <c r="B13" t="n">
         <v>57980</v>
@@ -2077,7 +2101,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499850</v>
+        <v>499846</v>
       </c>
       <c r="R13" t="n">
         <v>7003017</v>
@@ -2117,7 +2141,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2168,63 +2192,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849848</t>
+          <t>https://artportalen.se/Sighting/135849849</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849849</v>
+        <v>135849938</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>99614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499846</v>
+        <v>500061</v>
       </c>
       <c r="R14" t="n">
-        <v>7003017</v>
+        <v>7003131</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2259,43 +2279,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2312,67 +2308,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849849</t>
+          <t>https://artportalen.se/Sighting/135849938</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849871</v>
+        <v>135849939</v>
       </c>
       <c r="B15" t="n">
-        <v>58141</v>
+        <v>99614</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500027</v>
+        <v>500121</v>
       </c>
       <c r="R15" t="n">
-        <v>7003080</v>
+        <v>7003069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,28 +2395,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,67 +2424,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849871</t>
+          <t>https://artportalen.se/Sighting/135849939</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849872</v>
+        <v>135849940</v>
       </c>
       <c r="B16" t="n">
-        <v>58141</v>
+        <v>99614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499957</v>
+        <v>500102</v>
       </c>
       <c r="R16" t="n">
-        <v>7003085</v>
+        <v>7003063</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,17 +2511,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2573,16 +2540,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849872</t>
+          <t>https://artportalen.se/Sighting/135849940</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849868</v>
+        <v>135849941</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
+        <v>99614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,50 +2557,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500049</v>
+        <v>500056</v>
       </c>
       <c r="R17" t="n">
-        <v>7003051</v>
+        <v>7003057</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2668,28 +2627,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2706,13 +2656,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849868</t>
+          <t>https://artportalen.se/Sighting/135849941</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849938</v>
+        <v>135849942</v>
       </c>
       <c r="B18" t="n">
         <v>99614</v>
@@ -2755,10 +2705,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500061</v>
+        <v>500008</v>
       </c>
       <c r="R18" t="n">
-        <v>7003131</v>
+        <v>7003091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2822,13 +2772,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849938</t>
+          <t>https://artportalen.se/Sighting/135849942</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849939</v>
+        <v>135849943</v>
       </c>
       <c r="B19" t="n">
         <v>99614</v>
@@ -2871,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500121</v>
+        <v>500012</v>
       </c>
       <c r="R19" t="n">
-        <v>7003069</v>
+        <v>7003122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2938,13 +2888,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849939</t>
+          <t>https://artportalen.se/Sighting/135849943</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849940</v>
+        <v>135849946</v>
       </c>
       <c r="B20" t="n">
         <v>99614</v>
@@ -2987,10 +2937,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500102</v>
+        <v>500037</v>
       </c>
       <c r="R20" t="n">
-        <v>7003063</v>
+        <v>7003116</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3054,13 +3004,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849940</t>
+          <t>https://artportalen.se/Sighting/135849946</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849941</v>
+        <v>135849947</v>
       </c>
       <c r="B21" t="n">
         <v>99614</v>
@@ -3103,10 +3053,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500056</v>
+        <v>499954</v>
       </c>
       <c r="R21" t="n">
-        <v>7003057</v>
+        <v>7003072</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3170,13 +3120,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849941</t>
+          <t>https://artportalen.se/Sighting/135849947</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849942</v>
+        <v>135849948</v>
       </c>
       <c r="B22" t="n">
         <v>99614</v>
@@ -3219,10 +3169,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500008</v>
+        <v>499965</v>
       </c>
       <c r="R22" t="n">
-        <v>7003091</v>
+        <v>7003087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3286,16 +3236,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849942</t>
+          <t>https://artportalen.se/Sighting/135849948</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849943</v>
+        <v>135849924</v>
       </c>
       <c r="B23" t="n">
-        <v>99614</v>
+        <v>108364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,21 +3253,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3335,10 +3285,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500012</v>
+        <v>500117</v>
       </c>
       <c r="R23" t="n">
-        <v>7003122</v>
+        <v>7003169</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3385,7 +3335,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3402,16 +3352,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849943</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849945</v>
+        <v>135849925</v>
       </c>
       <c r="B24" t="n">
-        <v>99614</v>
+        <v>108364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3419,21 +3369,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3451,10 +3401,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500034</v>
+        <v>500067</v>
       </c>
       <c r="R24" t="n">
-        <v>7003139</v>
+        <v>7003124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3501,7 +3451,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3518,16 +3468,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849945</t>
+          <t>https://artportalen.se/Sighting/135849925</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849946</v>
+        <v>135849926</v>
       </c>
       <c r="B25" t="n">
-        <v>99614</v>
+        <v>108364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3535,21 +3485,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3567,10 +3517,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500037</v>
+        <v>500128</v>
       </c>
       <c r="R25" t="n">
-        <v>7003116</v>
+        <v>7003069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3634,16 +3584,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849946</t>
+          <t>https://artportalen.se/Sighting/135849926</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849947</v>
+        <v>135849927</v>
       </c>
       <c r="B26" t="n">
-        <v>99614</v>
+        <v>108364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3651,28 +3601,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3683,10 +3633,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499954</v>
+        <v>500012</v>
       </c>
       <c r="R26" t="n">
-        <v>7003072</v>
+        <v>7003082</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3750,16 +3700,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849947</t>
+          <t>https://artportalen.se/Sighting/135849927</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849948</v>
+        <v>135849929</v>
       </c>
       <c r="B27" t="n">
-        <v>99614</v>
+        <v>108364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3767,21 +3717,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3799,10 +3749,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499965</v>
+        <v>499925</v>
       </c>
       <c r="R27" t="n">
-        <v>7003087</v>
+        <v>7003078</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3866,16 +3816,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849948</t>
+          <t>https://artportalen.se/Sighting/135849929</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135850036</v>
+        <v>135849912</v>
       </c>
       <c r="B28" t="n">
-        <v>108294</v>
+        <v>111244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3883,21 +3833,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220083</v>
+        <v>220240</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3915,10 +3865,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499997</v>
+        <v>500036</v>
       </c>
       <c r="R28" t="n">
-        <v>7003107</v>
+        <v>7003072</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3982,45 +3932,53 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850036</t>
+          <t>https://artportalen.se/Sighting/135849912</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849924</v>
+        <v>135849986</v>
       </c>
       <c r="B29" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4031,10 +3989,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500117</v>
+        <v>500101</v>
       </c>
       <c r="R29" t="n">
-        <v>7003169</v>
+        <v>7003147</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4069,6 +4027,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4081,7 +4044,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4098,45 +4061,53 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849986</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849925</v>
+        <v>135849987</v>
       </c>
       <c r="B30" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -4147,10 +4118,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500067</v>
+        <v>500113</v>
       </c>
       <c r="R30" t="n">
-        <v>7003124</v>
+        <v>7003091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4185,6 +4156,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4197,7 +4173,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4214,45 +4195,53 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849925</t>
+          <t>https://artportalen.se/Sighting/135849987</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849926</v>
+        <v>135849988</v>
       </c>
       <c r="B31" t="n">
-        <v>108364</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4263,10 +4252,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500128</v>
+        <v>500025</v>
       </c>
       <c r="R31" t="n">
-        <v>7003069</v>
+        <v>7003030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4301,6 +4290,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4330,16 +4324,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849926</t>
+          <t>https://artportalen.se/Sighting/135849988</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849927</v>
+        <v>135849888</v>
       </c>
       <c r="B32" t="n">
-        <v>108364</v>
+        <v>98138</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4347,30 +4341,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220102</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4369,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500012</v>
+        <v>500042</v>
       </c>
       <c r="R32" t="n">
-        <v>7003082</v>
+        <v>7003136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4417,6 +4407,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4446,16 +4441,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849927</t>
+          <t>https://artportalen.se/Sighting/135849888</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849928</v>
+        <v>135849999</v>
       </c>
       <c r="B33" t="n">
-        <v>108364</v>
+        <v>98327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4463,28 +4458,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4495,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500037</v>
+        <v>500192</v>
       </c>
       <c r="R33" t="n">
-        <v>7003122</v>
+        <v>7003171</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4562,16 +4557,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849928</t>
+          <t>https://artportalen.se/Sighting/135849999</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849929</v>
+        <v>135850000</v>
       </c>
       <c r="B34" t="n">
-        <v>108364</v>
+        <v>98327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4579,21 +4574,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499925</v>
+        <v>500105</v>
       </c>
       <c r="R34" t="n">
-        <v>7003078</v>
+        <v>7003131</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4678,16 +4673,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849929</t>
+          <t>https://artportalen.se/Sighting/135850000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849912</v>
+        <v>135850002</v>
       </c>
       <c r="B35" t="n">
-        <v>111244</v>
+        <v>98327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4695,21 +4690,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220240</v>
+        <v>223358</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500036</v>
+        <v>500005</v>
       </c>
       <c r="R35" t="n">
-        <v>7003072</v>
+        <v>7003116</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4794,53 +4789,45 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849912</t>
+          <t>https://artportalen.se/Sighting/135850002</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849986</v>
+        <v>135850003</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>98327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4851,10 +4838,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500101</v>
+        <v>500039</v>
       </c>
       <c r="R36" t="n">
-        <v>7003147</v>
+        <v>7003109</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4889,11 +4876,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4923,53 +4905,45 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849986</t>
+          <t>https://artportalen.se/Sighting/135850003</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849987</v>
+        <v>135850005</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>98327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4980,10 +4954,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500113</v>
+        <v>499962</v>
       </c>
       <c r="R37" t="n">
-        <v>7003091</v>
+        <v>7003092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5018,11 +4992,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5035,12 +5004,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5057,53 +5021,45 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849987</t>
+          <t>https://artportalen.se/Sighting/135850005</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849988</v>
+        <v>135850006</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>98327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5114,10 +5070,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500025</v>
+        <v>499967</v>
       </c>
       <c r="R38" t="n">
-        <v>7003030</v>
+        <v>7003113</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5152,11 +5108,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5186,16 +5137,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849988</t>
+          <t>https://artportalen.se/Sighting/135850006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849865</v>
+        <v>135849905</v>
       </c>
       <c r="B39" t="n">
-        <v>110014</v>
+        <v>101375</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5203,28 +5154,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221184</v>
+        <v>224885</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -5235,10 +5186,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500092</v>
+        <v>500037</v>
       </c>
       <c r="R39" t="n">
-        <v>7003061</v>
+        <v>7003121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5302,16 +5253,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849865</t>
+          <t>https://artportalen.se/Sighting/135849905</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849866</v>
+        <v>135849906</v>
       </c>
       <c r="B40" t="n">
-        <v>110014</v>
+        <v>101375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5319,28 +5270,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221184</v>
+        <v>224885</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5351,10 +5302,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500055</v>
+        <v>500014</v>
       </c>
       <c r="R40" t="n">
-        <v>7003061</v>
+        <v>7003143</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5417,1631 +5368,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849866</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135849888</v>
-      </c>
-      <c r="B41" t="n">
-        <v>98138</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>500042</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849888</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135849890</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>500078</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7003109</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849890</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135849891</v>
-      </c>
-      <c r="B43" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>499954</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7003071</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849891</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>135849999</v>
-      </c>
-      <c r="B44" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>500192</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7003171</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849999</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>135850000</v>
-      </c>
-      <c r="B45" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>500105</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7003131</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850000</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>135850001</v>
-      </c>
-      <c r="B46" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>500070</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7003120</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850001</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>135850002</v>
-      </c>
-      <c r="B47" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>500005</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7003116</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850002</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135850003</v>
-      </c>
-      <c r="B48" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>500039</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7003109</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850003</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>135850005</v>
-      </c>
-      <c r="B49" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>499962</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7003092</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850005</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>135850006</v>
-      </c>
-      <c r="B50" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>499967</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7003113</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>135849874</v>
-      </c>
-      <c r="B51" t="n">
-        <v>102022</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>223366</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Svarta vinbär</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Ribes nigrum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>500036</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7003135</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849874</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>135849904</v>
-      </c>
-      <c r="B52" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>500029</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849904</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>135849905</v>
-      </c>
-      <c r="B53" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>500037</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7003121</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849905</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849906</v>
-      </c>
-      <c r="B54" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>500014</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003143</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849906</t>
         </is>
@@ -7088,20 +5414,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1495,65 +1495,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849879</v>
+        <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>57977</v>
+        <v>80556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500051</v>
+        <v>499900</v>
       </c>
       <c r="R9" t="n">
-        <v>7003122</v>
+        <v>7003040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,18 +1575,24 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1616,33 +1609,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849879</t>
+          <t>https://artportalen.se/Sighting/135849908</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849846</v>
+        <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1650,12 +1643,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1669,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500028</v>
+        <v>500051</v>
       </c>
       <c r="R10" t="n">
-        <v>7003043</v>
+        <v>7003122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,11 +1708,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1724,26 +1720,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1760,13 +1736,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849846</t>
+          <t>https://artportalen.se/Sighting/135849879</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849847</v>
+        <v>135849846</v>
       </c>
       <c r="B11" t="n">
         <v>57980</v>
@@ -1813,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499895</v>
+        <v>500028</v>
       </c>
       <c r="R11" t="n">
-        <v>7003040</v>
+        <v>7003043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1829,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,13 +1880,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849847</t>
+          <t>https://artportalen.se/Sighting/135849846</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849848</v>
+        <v>135849847</v>
       </c>
       <c r="B12" t="n">
         <v>57980</v>
@@ -1957,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499850</v>
+        <v>499895</v>
       </c>
       <c r="R12" t="n">
-        <v>7003017</v>
+        <v>7003040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1997,7 +1973,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,13 +2024,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849848</t>
+          <t>https://artportalen.se/Sighting/135849847</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849849</v>
+        <v>135849848</v>
       </c>
       <c r="B13" t="n">
         <v>57980</v>
@@ -2101,7 +2077,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499846</v>
+        <v>499850</v>
       </c>
       <c r="R13" t="n">
         <v>7003017</v>
@@ -2141,7 +2117,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,59 +2168,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849849</t>
+          <t>https://artportalen.se/Sighting/135849848</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849938</v>
+        <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>99614</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500061</v>
+        <v>499846</v>
       </c>
       <c r="R14" t="n">
-        <v>7003131</v>
+        <v>7003017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2279,19 +2259,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2308,59 +2312,67 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849938</t>
+          <t>https://artportalen.se/Sighting/135849849</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849939</v>
+        <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>99614</v>
+        <v>58141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500121</v>
+        <v>500027</v>
       </c>
       <c r="R15" t="n">
-        <v>7003069</v>
+        <v>7003080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2395,19 +2407,28 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2424,59 +2445,67 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849939</t>
+          <t>https://artportalen.se/Sighting/135849871</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849940</v>
+        <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>99614</v>
+        <v>58141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500102</v>
+        <v>499957</v>
       </c>
       <c r="R16" t="n">
-        <v>7003063</v>
+        <v>7003085</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2511,13 +2540,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2540,16 +2573,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849940</t>
+          <t>https://artportalen.se/Sighting/135849872</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849941</v>
+        <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>99614</v>
+        <v>58136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,42 +2590,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500056</v>
+        <v>500049</v>
       </c>
       <c r="R17" t="n">
-        <v>7003057</v>
+        <v>7003051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,19 +2668,28 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2656,13 +2706,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849941</t>
+          <t>https://artportalen.se/Sighting/135849868</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849942</v>
+        <v>135849938</v>
       </c>
       <c r="B18" t="n">
         <v>99614</v>
@@ -2705,10 +2755,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500008</v>
+        <v>500061</v>
       </c>
       <c r="R18" t="n">
-        <v>7003091</v>
+        <v>7003131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2772,13 +2822,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849942</t>
+          <t>https://artportalen.se/Sighting/135849938</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849943</v>
+        <v>135849939</v>
       </c>
       <c r="B19" t="n">
         <v>99614</v>
@@ -2821,10 +2871,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500012</v>
+        <v>500121</v>
       </c>
       <c r="R19" t="n">
-        <v>7003122</v>
+        <v>7003069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2888,13 +2938,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849943</t>
+          <t>https://artportalen.se/Sighting/135849939</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849946</v>
+        <v>135849940</v>
       </c>
       <c r="B20" t="n">
         <v>99614</v>
@@ -2937,10 +2987,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500037</v>
+        <v>500102</v>
       </c>
       <c r="R20" t="n">
-        <v>7003116</v>
+        <v>7003063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3004,13 +3054,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849946</t>
+          <t>https://artportalen.se/Sighting/135849940</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849947</v>
+        <v>135849941</v>
       </c>
       <c r="B21" t="n">
         <v>99614</v>
@@ -3053,10 +3103,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499954</v>
+        <v>500056</v>
       </c>
       <c r="R21" t="n">
-        <v>7003072</v>
+        <v>7003057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3120,13 +3170,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849947</t>
+          <t>https://artportalen.se/Sighting/135849941</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849948</v>
+        <v>135849942</v>
       </c>
       <c r="B22" t="n">
         <v>99614</v>
@@ -3169,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499965</v>
+        <v>500008</v>
       </c>
       <c r="R22" t="n">
-        <v>7003087</v>
+        <v>7003091</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3236,16 +3286,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849948</t>
+          <t>https://artportalen.se/Sighting/135849942</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849924</v>
+        <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>108364</v>
+        <v>99614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3253,21 +3303,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3285,10 +3335,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500117</v>
+        <v>500012</v>
       </c>
       <c r="R23" t="n">
-        <v>7003169</v>
+        <v>7003122</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3335,7 +3385,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3352,16 +3402,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849943</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849925</v>
+        <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>108364</v>
+        <v>99614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3369,21 +3419,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3401,10 +3451,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500067</v>
+        <v>500034</v>
       </c>
       <c r="R24" t="n">
-        <v>7003124</v>
+        <v>7003139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,7 +3501,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3468,16 +3518,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849925</t>
+          <t>https://artportalen.se/Sighting/135849945</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849926</v>
+        <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>108364</v>
+        <v>99614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3485,21 +3535,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3517,10 +3567,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500128</v>
+        <v>500037</v>
       </c>
       <c r="R25" t="n">
-        <v>7003069</v>
+        <v>7003116</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3584,16 +3634,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849926</t>
+          <t>https://artportalen.se/Sighting/135849946</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849927</v>
+        <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>108364</v>
+        <v>99614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,28 +3651,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3633,10 +3683,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500012</v>
+        <v>499954</v>
       </c>
       <c r="R26" t="n">
-        <v>7003082</v>
+        <v>7003072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3700,16 +3750,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849927</t>
+          <t>https://artportalen.se/Sighting/135849947</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849929</v>
+        <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>108364</v>
+        <v>99614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,21 +3767,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3749,10 +3799,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499925</v>
+        <v>499965</v>
       </c>
       <c r="R27" t="n">
-        <v>7003078</v>
+        <v>7003087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3816,16 +3866,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849929</t>
+          <t>https://artportalen.se/Sighting/135849948</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849912</v>
+        <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>111244</v>
+        <v>108294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,21 +3883,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3865,10 +3915,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500036</v>
+        <v>499997</v>
       </c>
       <c r="R28" t="n">
-        <v>7003072</v>
+        <v>7003107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3932,53 +3982,45 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849912</t>
+          <t>https://artportalen.se/Sighting/135850036</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849986</v>
+        <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -3989,10 +4031,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500101</v>
+        <v>500117</v>
       </c>
       <c r="R29" t="n">
-        <v>7003147</v>
+        <v>7003169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4027,11 +4069,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4081,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4061,53 +4098,45 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849986</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849987</v>
+        <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -4118,10 +4147,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500113</v>
+        <v>500067</v>
       </c>
       <c r="R30" t="n">
-        <v>7003091</v>
+        <v>7003124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4156,11 +4185,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4173,12 +4197,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4195,53 +4214,45 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849987</t>
+          <t>https://artportalen.se/Sighting/135849925</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849988</v>
+        <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>108364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4252,10 +4263,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500025</v>
+        <v>500128</v>
       </c>
       <c r="R31" t="n">
-        <v>7003030</v>
+        <v>7003069</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4290,11 +4301,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4324,16 +4330,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849988</t>
+          <t>https://artportalen.se/Sighting/135849926</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849888</v>
+        <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>98138</v>
+        <v>108364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4341,26 +4347,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4369,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500042</v>
+        <v>500012</v>
       </c>
       <c r="R32" t="n">
-        <v>7003136</v>
+        <v>7003082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4407,11 +4417,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4441,16 +4446,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849888</t>
+          <t>https://artportalen.se/Sighting/135849927</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849999</v>
+        <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>98327</v>
+        <v>108364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4458,28 +4463,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4490,10 +4495,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500192</v>
+        <v>500037</v>
       </c>
       <c r="R33" t="n">
-        <v>7003171</v>
+        <v>7003122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4557,16 +4562,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849999</t>
+          <t>https://artportalen.se/Sighting/135849928</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135850000</v>
+        <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>98327</v>
+        <v>108364</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4574,21 +4579,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500105</v>
+        <v>499925</v>
       </c>
       <c r="R34" t="n">
-        <v>7003131</v>
+        <v>7003078</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4673,16 +4678,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850000</t>
+          <t>https://artportalen.se/Sighting/135849929</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135850002</v>
+        <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>98327</v>
+        <v>111244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4690,21 +4695,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223358</v>
+        <v>220240</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500005</v>
+        <v>500036</v>
       </c>
       <c r="R35" t="n">
-        <v>7003116</v>
+        <v>7003072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4789,45 +4794,53 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850002</t>
+          <t>https://artportalen.se/Sighting/135849912</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850003</v>
+        <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>98327</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4838,10 +4851,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500039</v>
+        <v>500101</v>
       </c>
       <c r="R36" t="n">
-        <v>7003109</v>
+        <v>7003147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4876,6 +4889,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4905,45 +4923,53 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850003</t>
+          <t>https://artportalen.se/Sighting/135849986</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135850005</v>
+        <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>98327</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4954,10 +4980,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499962</v>
+        <v>500113</v>
       </c>
       <c r="R37" t="n">
-        <v>7003092</v>
+        <v>7003091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4992,6 +5018,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5004,7 +5035,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5021,45 +5057,53 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850005</t>
+          <t>https://artportalen.se/Sighting/135849987</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135850006</v>
+        <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>98327</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5070,10 +5114,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499967</v>
+        <v>500025</v>
       </c>
       <c r="R38" t="n">
-        <v>7003113</v>
+        <v>7003030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,6 +5152,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5137,16 +5186,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
+          <t>https://artportalen.se/Sighting/135849988</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849905</v>
+        <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>101375</v>
+        <v>110014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5154,28 +5203,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224885</v>
+        <v>221184</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -5186,10 +5235,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500037</v>
+        <v>500092</v>
       </c>
       <c r="R39" t="n">
-        <v>7003121</v>
+        <v>7003061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,16 +5302,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849905</t>
+          <t>https://artportalen.se/Sighting/135849865</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849906</v>
+        <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>101375</v>
+        <v>110014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5270,28 +5319,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224885</v>
+        <v>221184</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5302,10 +5351,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500014</v>
+        <v>500055</v>
       </c>
       <c r="R40" t="n">
-        <v>7003143</v>
+        <v>7003061</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5368,6 +5417,1631 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849866</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135849888</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>500042</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849888</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135849890</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>500078</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849890</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135849891</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>499954</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7003071</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849891</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135849999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>500192</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7003171</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849999</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135850000</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>500105</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7003131</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135850001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>500070</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7003120</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850001</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135850002</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>500005</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7003116</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850002</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135850003</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500039</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850003</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135850005</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>499962</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7003092</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850005</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135850006</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>499967</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7003113</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850006</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135849874</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102022</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500036</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7003135</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849874</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135849904</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849904</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135849905</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7003121</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849905</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849906</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500014</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003143</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849906</t>
         </is>
@@ -5414,6 +7088,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,52 +1495,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849908</v>
+        <v>135849879</v>
       </c>
       <c r="B9" t="n">
-        <v>80556</v>
+        <v>57979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499900</v>
+        <v>500051</v>
       </c>
       <c r="R9" t="n">
-        <v>7003040</v>
+        <v>7003122</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,24 +1588,18 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1609,33 +1616,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849908</t>
+          <t>https://artportalen.se/Sighting/135849879</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849879</v>
+        <v>135849846</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1643,20 +1650,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1670,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500051</v>
+        <v>500028</v>
       </c>
       <c r="R10" t="n">
-        <v>7003122</v>
+        <v>7003043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,6 +1707,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1720,6 +1724,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1736,16 +1760,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849879</t>
+          <t>https://artportalen.se/Sighting/135849846</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849846</v>
+        <v>135849847</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500028</v>
+        <v>499895</v>
       </c>
       <c r="R11" t="n">
-        <v>7003043</v>
+        <v>7003040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1853,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,16 +1904,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849846</t>
+          <t>https://artportalen.se/Sighting/135849847</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849847</v>
+        <v>135849848</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,10 +1957,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499895</v>
+        <v>499850</v>
       </c>
       <c r="R12" t="n">
-        <v>7003040</v>
+        <v>7003017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1973,7 +1997,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,16 +2048,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849847</t>
+          <t>https://artportalen.se/Sighting/135849848</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849848</v>
+        <v>135849849</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2101,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499850</v>
+        <v>499846</v>
       </c>
       <c r="R13" t="n">
         <v>7003017</v>
@@ -2117,7 +2141,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2168,63 +2192,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849848</t>
+          <t>https://artportalen.se/Sighting/135849849</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849849</v>
+        <v>135849938</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>99631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499846</v>
+        <v>500061</v>
       </c>
       <c r="R14" t="n">
-        <v>7003017</v>
+        <v>7003131</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2259,43 +2279,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2312,67 +2308,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849849</t>
+          <t>https://artportalen.se/Sighting/135849938</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849871</v>
+        <v>135849939</v>
       </c>
       <c r="B15" t="n">
-        <v>58141</v>
+        <v>99631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500027</v>
+        <v>500121</v>
       </c>
       <c r="R15" t="n">
-        <v>7003080</v>
+        <v>7003069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,28 +2395,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,67 +2424,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849871</t>
+          <t>https://artportalen.se/Sighting/135849939</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849872</v>
+        <v>135849940</v>
       </c>
       <c r="B16" t="n">
-        <v>58141</v>
+        <v>99631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499957</v>
+        <v>500102</v>
       </c>
       <c r="R16" t="n">
-        <v>7003085</v>
+        <v>7003063</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,17 +2511,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2573,16 +2540,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849872</t>
+          <t>https://artportalen.se/Sighting/135849940</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849868</v>
+        <v>135849941</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
+        <v>99631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,50 +2557,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500049</v>
+        <v>500056</v>
       </c>
       <c r="R17" t="n">
-        <v>7003051</v>
+        <v>7003057</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2668,28 +2627,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2706,16 +2656,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849868</t>
+          <t>https://artportalen.se/Sighting/135849941</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849938</v>
+        <v>135849942</v>
       </c>
       <c r="B18" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2755,10 +2705,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500061</v>
+        <v>500008</v>
       </c>
       <c r="R18" t="n">
-        <v>7003131</v>
+        <v>7003091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2822,16 +2772,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849938</t>
+          <t>https://artportalen.se/Sighting/135849942</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849939</v>
+        <v>135849943</v>
       </c>
       <c r="B19" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2871,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500121</v>
+        <v>500012</v>
       </c>
       <c r="R19" t="n">
-        <v>7003069</v>
+        <v>7003122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2938,16 +2888,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849939</t>
+          <t>https://artportalen.se/Sighting/135849943</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849940</v>
+        <v>135849946</v>
       </c>
       <c r="B20" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2987,10 +2937,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500102</v>
+        <v>500037</v>
       </c>
       <c r="R20" t="n">
-        <v>7003063</v>
+        <v>7003116</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3054,16 +3004,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849940</t>
+          <t>https://artportalen.se/Sighting/135849946</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849941</v>
+        <v>135849947</v>
       </c>
       <c r="B21" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3103,10 +3053,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500056</v>
+        <v>499954</v>
       </c>
       <c r="R21" t="n">
-        <v>7003057</v>
+        <v>7003072</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3170,16 +3120,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849941</t>
+          <t>https://artportalen.se/Sighting/135849947</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849942</v>
+        <v>135849948</v>
       </c>
       <c r="B22" t="n">
-        <v>99614</v>
+        <v>99631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3219,10 +3169,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500008</v>
+        <v>499965</v>
       </c>
       <c r="R22" t="n">
-        <v>7003091</v>
+        <v>7003087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3286,16 +3236,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849942</t>
+          <t>https://artportalen.se/Sighting/135849948</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849943</v>
+        <v>135849924</v>
       </c>
       <c r="B23" t="n">
-        <v>99614</v>
+        <v>108387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,21 +3253,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3335,10 +3285,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500012</v>
+        <v>500117</v>
       </c>
       <c r="R23" t="n">
-        <v>7003122</v>
+        <v>7003169</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3385,7 +3335,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3402,16 +3352,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849943</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849945</v>
+        <v>135849925</v>
       </c>
       <c r="B24" t="n">
-        <v>99614</v>
+        <v>108387</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3419,21 +3369,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3451,10 +3401,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500034</v>
+        <v>500067</v>
       </c>
       <c r="R24" t="n">
-        <v>7003139</v>
+        <v>7003124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3501,7 +3451,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3518,16 +3468,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849945</t>
+          <t>https://artportalen.se/Sighting/135849925</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849946</v>
+        <v>135849926</v>
       </c>
       <c r="B25" t="n">
-        <v>99614</v>
+        <v>108387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3535,21 +3485,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3567,10 +3517,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500037</v>
+        <v>500128</v>
       </c>
       <c r="R25" t="n">
-        <v>7003116</v>
+        <v>7003069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3634,16 +3584,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849946</t>
+          <t>https://artportalen.se/Sighting/135849926</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849947</v>
+        <v>135849927</v>
       </c>
       <c r="B26" t="n">
-        <v>99614</v>
+        <v>108387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3651,28 +3601,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3683,10 +3633,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499954</v>
+        <v>500012</v>
       </c>
       <c r="R26" t="n">
-        <v>7003072</v>
+        <v>7003082</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3750,16 +3700,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849947</t>
+          <t>https://artportalen.se/Sighting/135849927</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849948</v>
+        <v>135849929</v>
       </c>
       <c r="B27" t="n">
-        <v>99614</v>
+        <v>108387</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3767,21 +3717,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3799,10 +3749,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499965</v>
+        <v>499925</v>
       </c>
       <c r="R27" t="n">
-        <v>7003087</v>
+        <v>7003078</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3866,16 +3816,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849948</t>
+          <t>https://artportalen.se/Sighting/135849929</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135850036</v>
+        <v>135849912</v>
       </c>
       <c r="B28" t="n">
-        <v>108294</v>
+        <v>111267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3883,21 +3833,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220083</v>
+        <v>220240</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3915,10 +3865,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499997</v>
+        <v>500036</v>
       </c>
       <c r="R28" t="n">
-        <v>7003107</v>
+        <v>7003072</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3982,45 +3932,53 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850036</t>
+          <t>https://artportalen.se/Sighting/135849912</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849924</v>
+        <v>135849986</v>
       </c>
       <c r="B29" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4031,10 +3989,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500117</v>
+        <v>500101</v>
       </c>
       <c r="R29" t="n">
-        <v>7003169</v>
+        <v>7003147</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4069,6 +4027,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4081,7 +4044,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4098,45 +4061,53 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849986</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849925</v>
+        <v>135849987</v>
       </c>
       <c r="B30" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -4147,10 +4118,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500067</v>
+        <v>500113</v>
       </c>
       <c r="R30" t="n">
-        <v>7003124</v>
+        <v>7003091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4185,6 +4156,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4197,7 +4173,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4214,45 +4195,53 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849925</t>
+          <t>https://artportalen.se/Sighting/135849987</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849926</v>
+        <v>135849988</v>
       </c>
       <c r="B31" t="n">
-        <v>108364</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4263,10 +4252,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500128</v>
+        <v>500025</v>
       </c>
       <c r="R31" t="n">
-        <v>7003069</v>
+        <v>7003030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4301,6 +4290,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4330,16 +4324,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849926</t>
+          <t>https://artportalen.se/Sighting/135849988</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849927</v>
+        <v>135849888</v>
       </c>
       <c r="B32" t="n">
-        <v>108364</v>
+        <v>98155</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4347,30 +4341,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220102</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4369,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500012</v>
+        <v>500042</v>
       </c>
       <c r="R32" t="n">
-        <v>7003082</v>
+        <v>7003136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4417,6 +4407,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4446,16 +4441,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849927</t>
+          <t>https://artportalen.se/Sighting/135849888</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849928</v>
+        <v>135849999</v>
       </c>
       <c r="B33" t="n">
-        <v>108364</v>
+        <v>98344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4463,28 +4458,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4495,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500037</v>
+        <v>500192</v>
       </c>
       <c r="R33" t="n">
-        <v>7003122</v>
+        <v>7003171</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4562,16 +4557,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849928</t>
+          <t>https://artportalen.se/Sighting/135849999</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849929</v>
+        <v>135850000</v>
       </c>
       <c r="B34" t="n">
-        <v>108364</v>
+        <v>98344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4579,21 +4574,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499925</v>
+        <v>500105</v>
       </c>
       <c r="R34" t="n">
-        <v>7003078</v>
+        <v>7003131</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4678,16 +4673,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849929</t>
+          <t>https://artportalen.se/Sighting/135850000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849912</v>
+        <v>135850002</v>
       </c>
       <c r="B35" t="n">
-        <v>111244</v>
+        <v>98344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4695,21 +4690,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220240</v>
+        <v>223358</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500036</v>
+        <v>500005</v>
       </c>
       <c r="R35" t="n">
-        <v>7003072</v>
+        <v>7003116</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4794,53 +4789,45 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849912</t>
+          <t>https://artportalen.se/Sighting/135850002</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849986</v>
+        <v>135850003</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>98344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4851,10 +4838,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500101</v>
+        <v>500039</v>
       </c>
       <c r="R36" t="n">
-        <v>7003147</v>
+        <v>7003109</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4889,11 +4876,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4923,53 +4905,45 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849986</t>
+          <t>https://artportalen.se/Sighting/135850003</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849987</v>
+        <v>135850005</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>98344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4980,10 +4954,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500113</v>
+        <v>499962</v>
       </c>
       <c r="R37" t="n">
-        <v>7003091</v>
+        <v>7003092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5018,11 +4992,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5035,12 +5004,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5057,53 +5021,45 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849987</t>
+          <t>https://artportalen.se/Sighting/135850005</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849988</v>
+        <v>135850006</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>98344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5114,10 +5070,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500025</v>
+        <v>499967</v>
       </c>
       <c r="R38" t="n">
-        <v>7003030</v>
+        <v>7003113</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5152,11 +5108,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5186,16 +5137,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849988</t>
+          <t>https://artportalen.se/Sighting/135850006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849865</v>
+        <v>135849905</v>
       </c>
       <c r="B39" t="n">
-        <v>110014</v>
+        <v>101392</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5203,28 +5154,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221184</v>
+        <v>224885</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -5235,10 +5186,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500092</v>
+        <v>500037</v>
       </c>
       <c r="R39" t="n">
-        <v>7003061</v>
+        <v>7003121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5302,16 +5253,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849865</t>
+          <t>https://artportalen.se/Sighting/135849905</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849866</v>
+        <v>135849906</v>
       </c>
       <c r="B40" t="n">
-        <v>110014</v>
+        <v>101392</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5319,28 +5270,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221184</v>
+        <v>224885</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5351,10 +5302,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500055</v>
+        <v>500014</v>
       </c>
       <c r="R40" t="n">
-        <v>7003061</v>
+        <v>7003143</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5417,1631 +5368,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849866</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135849888</v>
-      </c>
-      <c r="B41" t="n">
-        <v>98138</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>500042</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849888</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135849890</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>500078</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7003109</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849890</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135849891</v>
-      </c>
-      <c r="B43" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>499954</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7003071</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849891</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>135849999</v>
-      </c>
-      <c r="B44" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>500192</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7003171</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849999</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>135850000</v>
-      </c>
-      <c r="B45" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>500105</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7003131</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850000</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>135850001</v>
-      </c>
-      <c r="B46" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>500070</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7003120</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850001</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>135850002</v>
-      </c>
-      <c r="B47" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>500005</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7003116</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850002</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135850003</v>
-      </c>
-      <c r="B48" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>500039</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7003109</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850003</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>135850005</v>
-      </c>
-      <c r="B49" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>499962</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7003092</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850005</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>135850006</v>
-      </c>
-      <c r="B50" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>499967</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7003113</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>135849874</v>
-      </c>
-      <c r="B51" t="n">
-        <v>102022</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>223366</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Svarta vinbär</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Ribes nigrum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>500036</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7003135</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849874</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>135849904</v>
-      </c>
-      <c r="B52" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>500029</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849904</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>135849905</v>
-      </c>
-      <c r="B53" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>500037</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7003121</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849905</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849906</v>
-      </c>
-      <c r="B54" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>500014</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003143</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849906</t>
         </is>
@@ -7088,20 +5414,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1495,65 +1495,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849879</v>
+        <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>57979</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500051</v>
+        <v>499900</v>
       </c>
       <c r="R9" t="n">
-        <v>7003122</v>
+        <v>7003040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,18 +1575,24 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1616,33 +1609,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849879</t>
+          <t>https://artportalen.se/Sighting/135849908</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849846</v>
+        <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1650,12 +1643,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1669,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500028</v>
+        <v>500051</v>
       </c>
       <c r="R10" t="n">
-        <v>7003043</v>
+        <v>7003122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,11 +1708,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1724,26 +1720,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1760,13 +1736,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849846</t>
+          <t>https://artportalen.se/Sighting/135849879</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849847</v>
+        <v>135849846</v>
       </c>
       <c r="B11" t="n">
         <v>57982</v>
@@ -1813,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499895</v>
+        <v>500028</v>
       </c>
       <c r="R11" t="n">
-        <v>7003040</v>
+        <v>7003043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1829,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,13 +1880,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849847</t>
+          <t>https://artportalen.se/Sighting/135849846</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849848</v>
+        <v>135849847</v>
       </c>
       <c r="B12" t="n">
         <v>57982</v>
@@ -1957,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499850</v>
+        <v>499895</v>
       </c>
       <c r="R12" t="n">
-        <v>7003017</v>
+        <v>7003040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1997,7 +1973,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,13 +2024,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849848</t>
+          <t>https://artportalen.se/Sighting/135849847</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849849</v>
+        <v>135849848</v>
       </c>
       <c r="B13" t="n">
         <v>57982</v>
@@ -2101,7 +2077,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499846</v>
+        <v>499850</v>
       </c>
       <c r="R13" t="n">
         <v>7003017</v>
@@ -2141,7 +2117,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,59 +2168,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849849</t>
+          <t>https://artportalen.se/Sighting/135849848</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849938</v>
+        <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>99631</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500061</v>
+        <v>499846</v>
       </c>
       <c r="R14" t="n">
-        <v>7003131</v>
+        <v>7003017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2279,19 +2259,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2308,59 +2312,67 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849938</t>
+          <t>https://artportalen.se/Sighting/135849849</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849939</v>
+        <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>99631</v>
+        <v>58143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500121</v>
+        <v>500027</v>
       </c>
       <c r="R15" t="n">
-        <v>7003069</v>
+        <v>7003080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2395,19 +2407,28 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2424,59 +2445,67 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849939</t>
+          <t>https://artportalen.se/Sighting/135849871</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849940</v>
+        <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>99631</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500102</v>
+        <v>499957</v>
       </c>
       <c r="R16" t="n">
-        <v>7003063</v>
+        <v>7003085</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2511,13 +2540,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2540,16 +2573,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849940</t>
+          <t>https://artportalen.se/Sighting/135849872</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849941</v>
+        <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>99631</v>
+        <v>58138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,42 +2590,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500056</v>
+        <v>500049</v>
       </c>
       <c r="R17" t="n">
-        <v>7003057</v>
+        <v>7003051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,19 +2668,28 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2656,13 +2706,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849941</t>
+          <t>https://artportalen.se/Sighting/135849868</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849942</v>
+        <v>135849938</v>
       </c>
       <c r="B18" t="n">
         <v>99631</v>
@@ -2705,10 +2755,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500008</v>
+        <v>500061</v>
       </c>
       <c r="R18" t="n">
-        <v>7003091</v>
+        <v>7003131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2772,13 +2822,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849942</t>
+          <t>https://artportalen.se/Sighting/135849938</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849943</v>
+        <v>135849939</v>
       </c>
       <c r="B19" t="n">
         <v>99631</v>
@@ -2821,10 +2871,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500012</v>
+        <v>500121</v>
       </c>
       <c r="R19" t="n">
-        <v>7003122</v>
+        <v>7003069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2888,13 +2938,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849943</t>
+          <t>https://artportalen.se/Sighting/135849939</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849946</v>
+        <v>135849940</v>
       </c>
       <c r="B20" t="n">
         <v>99631</v>
@@ -2937,10 +2987,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500037</v>
+        <v>500102</v>
       </c>
       <c r="R20" t="n">
-        <v>7003116</v>
+        <v>7003063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3004,13 +3054,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849946</t>
+          <t>https://artportalen.se/Sighting/135849940</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849947</v>
+        <v>135849941</v>
       </c>
       <c r="B21" t="n">
         <v>99631</v>
@@ -3053,10 +3103,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499954</v>
+        <v>500056</v>
       </c>
       <c r="R21" t="n">
-        <v>7003072</v>
+        <v>7003057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3120,13 +3170,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849947</t>
+          <t>https://artportalen.se/Sighting/135849941</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849948</v>
+        <v>135849942</v>
       </c>
       <c r="B22" t="n">
         <v>99631</v>
@@ -3169,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499965</v>
+        <v>500008</v>
       </c>
       <c r="R22" t="n">
-        <v>7003087</v>
+        <v>7003091</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3236,16 +3286,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849948</t>
+          <t>https://artportalen.se/Sighting/135849942</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849924</v>
+        <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>108387</v>
+        <v>99631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3253,21 +3303,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3285,10 +3335,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500117</v>
+        <v>500012</v>
       </c>
       <c r="R23" t="n">
-        <v>7003169</v>
+        <v>7003122</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3335,7 +3385,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3352,16 +3402,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849943</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849925</v>
+        <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>108387</v>
+        <v>99631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3369,21 +3419,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3401,10 +3451,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500067</v>
+        <v>500034</v>
       </c>
       <c r="R24" t="n">
-        <v>7003124</v>
+        <v>7003139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,7 +3501,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3468,16 +3518,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849925</t>
+          <t>https://artportalen.se/Sighting/135849945</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849926</v>
+        <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>108387</v>
+        <v>99631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3485,21 +3535,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3517,10 +3567,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500128</v>
+        <v>500037</v>
       </c>
       <c r="R25" t="n">
-        <v>7003069</v>
+        <v>7003116</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3584,16 +3634,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849926</t>
+          <t>https://artportalen.se/Sighting/135849946</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849927</v>
+        <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>108387</v>
+        <v>99631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,28 +3651,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3633,10 +3683,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500012</v>
+        <v>499954</v>
       </c>
       <c r="R26" t="n">
-        <v>7003082</v>
+        <v>7003072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3700,16 +3750,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849927</t>
+          <t>https://artportalen.se/Sighting/135849947</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849929</v>
+        <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>108387</v>
+        <v>99631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,21 +3767,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3749,10 +3799,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499925</v>
+        <v>499965</v>
       </c>
       <c r="R27" t="n">
-        <v>7003078</v>
+        <v>7003087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3816,16 +3866,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849929</t>
+          <t>https://artportalen.se/Sighting/135849948</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849912</v>
+        <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>111267</v>
+        <v>108317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,21 +3883,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3865,10 +3915,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500036</v>
+        <v>499997</v>
       </c>
       <c r="R28" t="n">
-        <v>7003072</v>
+        <v>7003107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3932,53 +3982,45 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849912</t>
+          <t>https://artportalen.se/Sighting/135850036</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849986</v>
+        <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -3989,10 +4031,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500101</v>
+        <v>500117</v>
       </c>
       <c r="R29" t="n">
-        <v>7003147</v>
+        <v>7003169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4027,11 +4069,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4081,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4061,53 +4098,45 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849986</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849987</v>
+        <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -4118,10 +4147,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500113</v>
+        <v>500067</v>
       </c>
       <c r="R30" t="n">
-        <v>7003091</v>
+        <v>7003124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4156,11 +4185,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4173,12 +4197,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4195,53 +4214,45 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849987</t>
+          <t>https://artportalen.se/Sighting/135849925</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849988</v>
+        <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>108387</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4252,10 +4263,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500025</v>
+        <v>500128</v>
       </c>
       <c r="R31" t="n">
-        <v>7003030</v>
+        <v>7003069</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4290,11 +4301,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4324,16 +4330,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849988</t>
+          <t>https://artportalen.se/Sighting/135849926</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849888</v>
+        <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>98155</v>
+        <v>108387</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4341,26 +4347,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4369,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500042</v>
+        <v>500012</v>
       </c>
       <c r="R32" t="n">
-        <v>7003136</v>
+        <v>7003082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4407,11 +4417,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4441,16 +4446,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849888</t>
+          <t>https://artportalen.se/Sighting/135849927</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849999</v>
+        <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>98344</v>
+        <v>108387</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4458,28 +4463,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4490,10 +4495,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500192</v>
+        <v>500037</v>
       </c>
       <c r="R33" t="n">
-        <v>7003171</v>
+        <v>7003122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4557,16 +4562,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849999</t>
+          <t>https://artportalen.se/Sighting/135849928</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135850000</v>
+        <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>98344</v>
+        <v>108387</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4574,21 +4579,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500105</v>
+        <v>499925</v>
       </c>
       <c r="R34" t="n">
-        <v>7003131</v>
+        <v>7003078</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4673,16 +4678,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850000</t>
+          <t>https://artportalen.se/Sighting/135849929</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135850002</v>
+        <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>98344</v>
+        <v>111267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4690,21 +4695,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223358</v>
+        <v>220240</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500005</v>
+        <v>500036</v>
       </c>
       <c r="R35" t="n">
-        <v>7003116</v>
+        <v>7003072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4789,45 +4794,53 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850002</t>
+          <t>https://artportalen.se/Sighting/135849912</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850003</v>
+        <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>98344</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4838,10 +4851,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500039</v>
+        <v>500101</v>
       </c>
       <c r="R36" t="n">
-        <v>7003109</v>
+        <v>7003147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4876,6 +4889,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4905,45 +4923,53 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850003</t>
+          <t>https://artportalen.se/Sighting/135849986</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135850005</v>
+        <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>98344</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4954,10 +4980,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499962</v>
+        <v>500113</v>
       </c>
       <c r="R37" t="n">
-        <v>7003092</v>
+        <v>7003091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4992,6 +5018,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5004,7 +5035,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5021,45 +5057,53 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850005</t>
+          <t>https://artportalen.se/Sighting/135849987</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135850006</v>
+        <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>98344</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5070,10 +5114,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499967</v>
+        <v>500025</v>
       </c>
       <c r="R38" t="n">
-        <v>7003113</v>
+        <v>7003030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,6 +5152,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5137,16 +5186,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
+          <t>https://artportalen.se/Sighting/135849988</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849905</v>
+        <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>101392</v>
+        <v>110037</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5154,28 +5203,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224885</v>
+        <v>221184</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -5186,10 +5235,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500037</v>
+        <v>500092</v>
       </c>
       <c r="R39" t="n">
-        <v>7003121</v>
+        <v>7003061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,16 +5302,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849905</t>
+          <t>https://artportalen.se/Sighting/135849865</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849906</v>
+        <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>101392</v>
+        <v>110037</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5270,28 +5319,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224885</v>
+        <v>221184</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5302,10 +5351,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500014</v>
+        <v>500055</v>
       </c>
       <c r="R40" t="n">
-        <v>7003143</v>
+        <v>7003061</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5368,6 +5417,1631 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849866</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135849888</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98155</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>500042</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849888</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135849890</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>500078</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849890</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135849891</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>499954</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7003071</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849891</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135849999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>500192</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7003171</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849999</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135850000</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>500105</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7003131</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135850001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>500070</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7003120</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850001</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135850002</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>500005</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7003116</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850002</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135850003</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500039</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850003</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135850005</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>499962</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7003092</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850005</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135850006</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>499967</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7003113</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850006</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135849874</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102039</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500036</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7003135</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849874</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135849904</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849904</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135849905</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7003121</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849905</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849906</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500014</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003143</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849906</t>
         </is>
@@ -5414,6 +7088,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102039</v>
+        <v>102041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1495,52 +1495,65 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849908</v>
+        <v>135849879</v>
       </c>
       <c r="B9" t="n">
-        <v>80559</v>
+        <v>57979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499900</v>
+        <v>500051</v>
       </c>
       <c r="R9" t="n">
-        <v>7003040</v>
+        <v>7003122</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,24 +1588,18 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1609,33 +1616,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849908</t>
+          <t>https://artportalen.se/Sighting/135849879</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849879</v>
+        <v>135849846</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1643,20 +1650,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1670,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500051</v>
+        <v>500028</v>
       </c>
       <c r="R10" t="n">
-        <v>7003122</v>
+        <v>7003043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,6 +1707,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1720,6 +1724,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1736,13 +1760,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849879</t>
+          <t>https://artportalen.se/Sighting/135849846</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849846</v>
+        <v>135849847</v>
       </c>
       <c r="B11" t="n">
         <v>57982</v>
@@ -1789,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500028</v>
+        <v>499895</v>
       </c>
       <c r="R11" t="n">
-        <v>7003043</v>
+        <v>7003040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1853,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,13 +1904,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849846</t>
+          <t>https://artportalen.se/Sighting/135849847</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849847</v>
+        <v>135849848</v>
       </c>
       <c r="B12" t="n">
         <v>57982</v>
@@ -1933,10 +1957,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499895</v>
+        <v>499850</v>
       </c>
       <c r="R12" t="n">
-        <v>7003040</v>
+        <v>7003017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1973,7 +1997,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,13 +2048,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849847</t>
+          <t>https://artportalen.se/Sighting/135849848</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849848</v>
+        <v>135849849</v>
       </c>
       <c r="B13" t="n">
         <v>57982</v>
@@ -2077,7 +2101,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499850</v>
+        <v>499846</v>
       </c>
       <c r="R13" t="n">
         <v>7003017</v>
@@ -2117,7 +2141,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2168,63 +2192,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849848</t>
+          <t>https://artportalen.se/Sighting/135849849</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849849</v>
+        <v>135849938</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>99632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499846</v>
+        <v>500061</v>
       </c>
       <c r="R14" t="n">
-        <v>7003017</v>
+        <v>7003131</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2259,43 +2279,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2312,67 +2308,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849849</t>
+          <t>https://artportalen.se/Sighting/135849938</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849871</v>
+        <v>135849939</v>
       </c>
       <c r="B15" t="n">
-        <v>58143</v>
+        <v>99632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500027</v>
+        <v>500121</v>
       </c>
       <c r="R15" t="n">
-        <v>7003080</v>
+        <v>7003069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,28 +2395,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,67 +2424,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849871</t>
+          <t>https://artportalen.se/Sighting/135849939</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849872</v>
+        <v>135849940</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>99632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499957</v>
+        <v>500102</v>
       </c>
       <c r="R16" t="n">
-        <v>7003085</v>
+        <v>7003063</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2540,17 +2511,13 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2573,16 +2540,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849872</t>
+          <t>https://artportalen.se/Sighting/135849940</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849868</v>
+        <v>135849941</v>
       </c>
       <c r="B17" t="n">
-        <v>58138</v>
+        <v>99632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2590,50 +2557,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500049</v>
+        <v>500056</v>
       </c>
       <c r="R17" t="n">
-        <v>7003051</v>
+        <v>7003057</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2668,28 +2627,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Minst 1 individ med lockläte.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2706,13 +2656,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849868</t>
+          <t>https://artportalen.se/Sighting/135849941</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849938</v>
+        <v>135849942</v>
       </c>
       <c r="B18" t="n">
         <v>99632</v>
@@ -2755,10 +2705,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500061</v>
+        <v>500008</v>
       </c>
       <c r="R18" t="n">
-        <v>7003131</v>
+        <v>7003091</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2822,13 +2772,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849938</t>
+          <t>https://artportalen.se/Sighting/135849942</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849939</v>
+        <v>135849943</v>
       </c>
       <c r="B19" t="n">
         <v>99632</v>
@@ -2871,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500121</v>
+        <v>500012</v>
       </c>
       <c r="R19" t="n">
-        <v>7003069</v>
+        <v>7003122</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2938,13 +2888,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849939</t>
+          <t>https://artportalen.se/Sighting/135849943</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849940</v>
+        <v>135849946</v>
       </c>
       <c r="B20" t="n">
         <v>99632</v>
@@ -2987,10 +2937,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500102</v>
+        <v>500037</v>
       </c>
       <c r="R20" t="n">
-        <v>7003063</v>
+        <v>7003116</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3054,13 +3004,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849940</t>
+          <t>https://artportalen.se/Sighting/135849946</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849941</v>
+        <v>135849947</v>
       </c>
       <c r="B21" t="n">
         <v>99632</v>
@@ -3103,10 +3053,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500056</v>
+        <v>499954</v>
       </c>
       <c r="R21" t="n">
-        <v>7003057</v>
+        <v>7003072</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3170,13 +3120,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849941</t>
+          <t>https://artportalen.se/Sighting/135849947</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849942</v>
+        <v>135849948</v>
       </c>
       <c r="B22" t="n">
         <v>99632</v>
@@ -3219,10 +3169,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500008</v>
+        <v>499965</v>
       </c>
       <c r="R22" t="n">
-        <v>7003091</v>
+        <v>7003087</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3286,16 +3236,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849942</t>
+          <t>https://artportalen.se/Sighting/135849948</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849943</v>
+        <v>135849924</v>
       </c>
       <c r="B23" t="n">
-        <v>99632</v>
+        <v>108389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,21 +3253,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3335,10 +3285,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500012</v>
+        <v>500117</v>
       </c>
       <c r="R23" t="n">
-        <v>7003122</v>
+        <v>7003169</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3385,7 +3335,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3402,16 +3352,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849943</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849945</v>
+        <v>135849925</v>
       </c>
       <c r="B24" t="n">
-        <v>99632</v>
+        <v>108389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3419,21 +3369,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3451,10 +3401,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500034</v>
+        <v>500067</v>
       </c>
       <c r="R24" t="n">
-        <v>7003139</v>
+        <v>7003124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3501,7 +3451,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3518,16 +3468,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849945</t>
+          <t>https://artportalen.se/Sighting/135849925</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849946</v>
+        <v>135849926</v>
       </c>
       <c r="B25" t="n">
-        <v>99632</v>
+        <v>108389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3535,21 +3485,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3567,10 +3517,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500037</v>
+        <v>500128</v>
       </c>
       <c r="R25" t="n">
-        <v>7003116</v>
+        <v>7003069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3634,16 +3584,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849946</t>
+          <t>https://artportalen.se/Sighting/135849926</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849947</v>
+        <v>135849927</v>
       </c>
       <c r="B26" t="n">
-        <v>99632</v>
+        <v>108389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3651,28 +3601,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3683,10 +3633,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499954</v>
+        <v>500012</v>
       </c>
       <c r="R26" t="n">
-        <v>7003072</v>
+        <v>7003082</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3750,16 +3700,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849947</t>
+          <t>https://artportalen.se/Sighting/135849927</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849948</v>
+        <v>135849929</v>
       </c>
       <c r="B27" t="n">
-        <v>99632</v>
+        <v>108389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3767,21 +3717,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3799,10 +3749,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499965</v>
+        <v>499925</v>
       </c>
       <c r="R27" t="n">
-        <v>7003087</v>
+        <v>7003078</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3866,16 +3816,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849948</t>
+          <t>https://artportalen.se/Sighting/135849929</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135850036</v>
+        <v>135849912</v>
       </c>
       <c r="B28" t="n">
-        <v>108319</v>
+        <v>111269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3883,21 +3833,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220083</v>
+        <v>220240</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3915,10 +3865,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499997</v>
+        <v>500036</v>
       </c>
       <c r="R28" t="n">
-        <v>7003107</v>
+        <v>7003072</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3982,45 +3932,53 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850036</t>
+          <t>https://artportalen.se/Sighting/135849912</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849924</v>
+        <v>135849986</v>
       </c>
       <c r="B29" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4031,10 +3989,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500117</v>
+        <v>500101</v>
       </c>
       <c r="R29" t="n">
-        <v>7003169</v>
+        <v>7003147</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4069,6 +4027,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4081,7 +4044,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4098,45 +4061,53 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849986</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849925</v>
+        <v>135849987</v>
       </c>
       <c r="B30" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -4147,10 +4118,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500067</v>
+        <v>500113</v>
       </c>
       <c r="R30" t="n">
-        <v>7003124</v>
+        <v>7003091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4185,6 +4156,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4197,7 +4173,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4214,45 +4195,53 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849925</t>
+          <t>https://artportalen.se/Sighting/135849987</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849926</v>
+        <v>135849988</v>
       </c>
       <c r="B31" t="n">
-        <v>108389</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220102</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4263,10 +4252,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500128</v>
+        <v>500025</v>
       </c>
       <c r="R31" t="n">
-        <v>7003069</v>
+        <v>7003030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4301,6 +4290,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4330,16 +4324,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849926</t>
+          <t>https://artportalen.se/Sighting/135849988</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849927</v>
+        <v>135849888</v>
       </c>
       <c r="B32" t="n">
-        <v>108389</v>
+        <v>98156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4347,30 +4341,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220102</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4379,10 +4369,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500012</v>
+        <v>500042</v>
       </c>
       <c r="R32" t="n">
-        <v>7003082</v>
+        <v>7003136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4417,6 +4407,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4446,16 +4441,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849927</t>
+          <t>https://artportalen.se/Sighting/135849888</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849928</v>
+        <v>135849999</v>
       </c>
       <c r="B33" t="n">
-        <v>108389</v>
+        <v>98345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4463,28 +4458,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4495,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500037</v>
+        <v>500192</v>
       </c>
       <c r="R33" t="n">
-        <v>7003122</v>
+        <v>7003171</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4562,16 +4557,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849928</t>
+          <t>https://artportalen.se/Sighting/135849999</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849929</v>
+        <v>135850000</v>
       </c>
       <c r="B34" t="n">
-        <v>108389</v>
+        <v>98345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4579,21 +4574,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>499925</v>
+        <v>500105</v>
       </c>
       <c r="R34" t="n">
-        <v>7003078</v>
+        <v>7003131</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4678,16 +4673,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849929</t>
+          <t>https://artportalen.se/Sighting/135850000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849912</v>
+        <v>135850002</v>
       </c>
       <c r="B35" t="n">
-        <v>111269</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4695,21 +4690,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220240</v>
+        <v>223358</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500036</v>
+        <v>500005</v>
       </c>
       <c r="R35" t="n">
-        <v>7003072</v>
+        <v>7003116</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4794,53 +4789,45 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849912</t>
+          <t>https://artportalen.se/Sighting/135850002</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849986</v>
+        <v>135850003</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4851,10 +4838,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500101</v>
+        <v>500039</v>
       </c>
       <c r="R36" t="n">
-        <v>7003147</v>
+        <v>7003109</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4889,11 +4876,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4923,53 +4905,45 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849986</t>
+          <t>https://artportalen.se/Sighting/135850003</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849987</v>
+        <v>135850005</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>98345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4980,10 +4954,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500113</v>
+        <v>499962</v>
       </c>
       <c r="R37" t="n">
-        <v>7003091</v>
+        <v>7003092</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5018,11 +4992,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5035,12 +5004,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5057,53 +5021,45 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849987</t>
+          <t>https://artportalen.se/Sighting/135850005</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849988</v>
+        <v>135850006</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>223358</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5114,10 +5070,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500025</v>
+        <v>499967</v>
       </c>
       <c r="R38" t="n">
-        <v>7003030</v>
+        <v>7003113</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5152,11 +5108,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5186,16 +5137,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849988</t>
+          <t>https://artportalen.se/Sighting/135850006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849865</v>
+        <v>135849905</v>
       </c>
       <c r="B39" t="n">
-        <v>110039</v>
+        <v>101394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5203,28 +5154,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221184</v>
+        <v>224885</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -5235,10 +5186,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500092</v>
+        <v>500037</v>
       </c>
       <c r="R39" t="n">
-        <v>7003061</v>
+        <v>7003121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5302,16 +5253,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849865</t>
+          <t>https://artportalen.se/Sighting/135849905</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849866</v>
+        <v>135849906</v>
       </c>
       <c r="B40" t="n">
-        <v>110039</v>
+        <v>101394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5319,28 +5270,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221184</v>
+        <v>224885</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5351,10 +5302,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500055</v>
+        <v>500014</v>
       </c>
       <c r="R40" t="n">
-        <v>7003061</v>
+        <v>7003143</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5417,1631 +5368,6 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849866</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135849888</v>
-      </c>
-      <c r="B41" t="n">
-        <v>98156</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>500042</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849888</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135849890</v>
-      </c>
-      <c r="B42" t="n">
-        <v>99100</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>500078</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7003109</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849890</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135849891</v>
-      </c>
-      <c r="B43" t="n">
-        <v>99100</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>499954</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7003071</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849891</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>135849999</v>
-      </c>
-      <c r="B44" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>500192</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7003171</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849999</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>135850000</v>
-      </c>
-      <c r="B45" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>500105</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7003131</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850000</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>135850001</v>
-      </c>
-      <c r="B46" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>500070</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7003120</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850001</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>135850002</v>
-      </c>
-      <c r="B47" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>500005</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7003116</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850002</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135850003</v>
-      </c>
-      <c r="B48" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>500039</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7003109</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850003</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>135850005</v>
-      </c>
-      <c r="B49" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>499962</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7003092</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850005</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>135850006</v>
-      </c>
-      <c r="B50" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>499967</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7003113</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>135849874</v>
-      </c>
-      <c r="B51" t="n">
-        <v>102041</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>223366</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Svarta vinbär</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Ribes nigrum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>500036</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7003135</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849874</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>135849904</v>
-      </c>
-      <c r="B52" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>500029</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7003136</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849904</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>135849905</v>
-      </c>
-      <c r="B53" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>500037</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7003121</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849905</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849906</v>
-      </c>
-      <c r="B54" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>500014</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003143</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849906</t>
         </is>
@@ -7088,20 +5414,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1495,65 +1495,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135849879</v>
+        <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>57979</v>
+        <v>80559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500051</v>
+        <v>499900</v>
       </c>
       <c r="R9" t="n">
-        <v>7003122</v>
+        <v>7003040</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,18 +1575,24 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1616,33 +1609,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849879</t>
+          <t>https://artportalen.se/Sighting/135849908</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849846</v>
+        <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1650,12 +1643,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1669,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500028</v>
+        <v>500051</v>
       </c>
       <c r="R10" t="n">
-        <v>7003043</v>
+        <v>7003122</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,11 +1708,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1724,26 +1720,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1760,13 +1736,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849846</t>
+          <t>https://artportalen.se/Sighting/135849879</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849847</v>
+        <v>135849846</v>
       </c>
       <c r="B11" t="n">
         <v>57982</v>
@@ -1813,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499895</v>
+        <v>500028</v>
       </c>
       <c r="R11" t="n">
-        <v>7003040</v>
+        <v>7003043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1829,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,13 +1880,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849847</t>
+          <t>https://artportalen.se/Sighting/135849846</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849848</v>
+        <v>135849847</v>
       </c>
       <c r="B12" t="n">
         <v>57982</v>
@@ -1957,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499850</v>
+        <v>499895</v>
       </c>
       <c r="R12" t="n">
-        <v>7003017</v>
+        <v>7003040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1997,7 +1973,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, enstaka på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,13 +2024,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849848</t>
+          <t>https://artportalen.se/Sighting/135849847</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849849</v>
+        <v>135849848</v>
       </c>
       <c r="B13" t="n">
         <v>57982</v>
@@ -2101,7 +2077,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499846</v>
+        <v>499850</v>
       </c>
       <c r="R13" t="n">
         <v>7003017</v>
@@ -2141,7 +2117,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,59 +2168,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849849</t>
+          <t>https://artportalen.se/Sighting/135849848</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849938</v>
+        <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>99632</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500061</v>
+        <v>499846</v>
       </c>
       <c r="R14" t="n">
-        <v>7003131</v>
+        <v>7003017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2279,19 +2259,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och tydliga, längs flera meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2308,59 +2312,67 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849938</t>
+          <t>https://artportalen.se/Sighting/135849849</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849939</v>
+        <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>99632</v>
+        <v>58143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500121</v>
+        <v>500027</v>
       </c>
       <c r="R15" t="n">
-        <v>7003069</v>
+        <v>7003080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2395,19 +2407,28 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2424,59 +2445,67 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849939</t>
+          <t>https://artportalen.se/Sighting/135849871</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849940</v>
+        <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>99632</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500102</v>
+        <v>499957</v>
       </c>
       <c r="R16" t="n">
-        <v>7003063</v>
+        <v>7003085</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2511,13 +2540,17 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2540,16 +2573,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849940</t>
+          <t>https://artportalen.se/Sighting/135849872</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849941</v>
+        <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>99632</v>
+        <v>58138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,42 +2590,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>103023</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500056</v>
+        <v>500049</v>
       </c>
       <c r="R17" t="n">
-        <v>7003057</v>
+        <v>7003051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,19 +2668,28 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad skog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2656,16 +2706,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849941</t>
+          <t>https://artportalen.se/Sighting/135849868</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849942</v>
+        <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,10 +2755,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500008</v>
+        <v>500061</v>
       </c>
       <c r="R18" t="n">
-        <v>7003091</v>
+        <v>7003131</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2772,16 +2822,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849942</t>
+          <t>https://artportalen.se/Sighting/135849938</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849943</v>
+        <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,10 +2871,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500012</v>
+        <v>500121</v>
       </c>
       <c r="R19" t="n">
-        <v>7003122</v>
+        <v>7003069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2888,16 +2938,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849943</t>
+          <t>https://artportalen.se/Sighting/135849939</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849946</v>
+        <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,10 +2987,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500037</v>
+        <v>500102</v>
       </c>
       <c r="R20" t="n">
-        <v>7003116</v>
+        <v>7003063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3004,16 +3054,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849946</t>
+          <t>https://artportalen.se/Sighting/135849940</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849947</v>
+        <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,10 +3103,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499954</v>
+        <v>500056</v>
       </c>
       <c r="R21" t="n">
-        <v>7003072</v>
+        <v>7003057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3120,16 +3170,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849947</t>
+          <t>https://artportalen.se/Sighting/135849941</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849948</v>
+        <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99632</v>
+        <v>99633</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3169,10 +3219,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499965</v>
+        <v>500008</v>
       </c>
       <c r="R22" t="n">
-        <v>7003087</v>
+        <v>7003091</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3236,16 +3286,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849948</t>
+          <t>https://artportalen.se/Sighting/135849942</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849924</v>
+        <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>108389</v>
+        <v>99633</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3253,21 +3303,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3285,10 +3335,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500117</v>
+        <v>500012</v>
       </c>
       <c r="R23" t="n">
-        <v>7003169</v>
+        <v>7003122</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3335,7 +3385,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3352,16 +3402,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849924</t>
+          <t>https://artportalen.se/Sighting/135849943</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849925</v>
+        <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>108389</v>
+        <v>99633</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3369,21 +3419,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3401,10 +3451,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500067</v>
+        <v>500034</v>
       </c>
       <c r="R24" t="n">
-        <v>7003124</v>
+        <v>7003139</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,7 +3501,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3468,16 +3518,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849925</t>
+          <t>https://artportalen.se/Sighting/135849945</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849926</v>
+        <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>108389</v>
+        <v>99633</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3485,21 +3535,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3517,10 +3567,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500128</v>
+        <v>500037</v>
       </c>
       <c r="R25" t="n">
-        <v>7003069</v>
+        <v>7003116</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3584,16 +3634,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849926</t>
+          <t>https://artportalen.se/Sighting/135849946</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849927</v>
+        <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>108389</v>
+        <v>99633</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,28 +3651,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3633,10 +3683,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500012</v>
+        <v>499954</v>
       </c>
       <c r="R26" t="n">
-        <v>7003082</v>
+        <v>7003072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3700,16 +3750,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849927</t>
+          <t>https://artportalen.se/Sighting/135849947</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849929</v>
+        <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>108389</v>
+        <v>99633</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,21 +3767,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3749,10 +3799,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499925</v>
+        <v>499965</v>
       </c>
       <c r="R27" t="n">
-        <v>7003078</v>
+        <v>7003087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3816,16 +3866,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849929</t>
+          <t>https://artportalen.se/Sighting/135849948</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849912</v>
+        <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>111269</v>
+        <v>108320</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,21 +3883,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3865,10 +3915,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500036</v>
+        <v>499997</v>
       </c>
       <c r="R28" t="n">
-        <v>7003072</v>
+        <v>7003107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3932,53 +3982,45 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849912</t>
+          <t>https://artportalen.se/Sighting/135850036</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849986</v>
+        <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -3989,10 +4031,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500101</v>
+        <v>500117</v>
       </c>
       <c r="R29" t="n">
-        <v>7003147</v>
+        <v>7003169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4027,11 +4069,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4044,7 +4081,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4061,53 +4098,45 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849986</t>
+          <t>https://artportalen.se/Sighting/135849924</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849987</v>
+        <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -4118,10 +4147,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500113</v>
+        <v>500067</v>
       </c>
       <c r="R30" t="n">
-        <v>7003091</v>
+        <v>7003124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4156,11 +4185,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4173,12 +4197,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4195,53 +4214,45 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849987</t>
+          <t>https://artportalen.se/Sighting/135849925</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849988</v>
+        <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>108390</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4252,10 +4263,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500025</v>
+        <v>500128</v>
       </c>
       <c r="R31" t="n">
-        <v>7003030</v>
+        <v>7003069</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4290,11 +4301,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4324,16 +4330,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849988</t>
+          <t>https://artportalen.se/Sighting/135849926</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849888</v>
+        <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>98156</v>
+        <v>108390</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4341,26 +4347,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220102</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -4369,10 +4379,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500042</v>
+        <v>500012</v>
       </c>
       <c r="R32" t="n">
-        <v>7003136</v>
+        <v>7003082</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4407,11 +4417,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4441,16 +4446,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849888</t>
+          <t>https://artportalen.se/Sighting/135849927</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849999</v>
+        <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>98345</v>
+        <v>108390</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4458,28 +4463,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4490,10 +4495,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500192</v>
+        <v>500037</v>
       </c>
       <c r="R33" t="n">
-        <v>7003171</v>
+        <v>7003122</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4557,16 +4562,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849999</t>
+          <t>https://artportalen.se/Sighting/135849928</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135850000</v>
+        <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>108390</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4574,21 +4579,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500105</v>
+        <v>499925</v>
       </c>
       <c r="R34" t="n">
-        <v>7003131</v>
+        <v>7003078</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4673,16 +4678,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850000</t>
+          <t>https://artportalen.se/Sighting/135849929</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135850002</v>
+        <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>111270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4690,21 +4695,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223358</v>
+        <v>220240</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500005</v>
+        <v>500036</v>
       </c>
       <c r="R35" t="n">
-        <v>7003116</v>
+        <v>7003072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4789,45 +4794,53 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850002</t>
+          <t>https://artportalen.se/Sighting/135849912</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850003</v>
+        <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4838,10 +4851,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500039</v>
+        <v>500101</v>
       </c>
       <c r="R36" t="n">
-        <v>7003109</v>
+        <v>7003147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4876,6 +4889,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor och 5 blomställningar inom ca 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4905,45 +4923,53 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850003</t>
+          <t>https://artportalen.se/Sighting/135849986</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135850005</v>
+        <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4954,10 +4980,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>499962</v>
+        <v>500113</v>
       </c>
       <c r="R37" t="n">
-        <v>7003092</v>
+        <v>7003091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4992,6 +5018,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor och 1 blomställning inom ca 0,3 m2 yta i grandominerad barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5004,7 +5035,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Grandominerad bitvis flerskiktad barrblandskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5021,45 +5057,53 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850005</t>
+          <t>https://artportalen.se/Sighting/135849987</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135850006</v>
+        <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>99295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5070,10 +5114,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>499967</v>
+        <v>500025</v>
       </c>
       <c r="R38" t="n">
-        <v>7003113</v>
+        <v>7003030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,6 +5152,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor och 1 blomställning inom 0,3 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5137,16 +5186,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850006</t>
+          <t>https://artportalen.se/Sighting/135849988</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849905</v>
+        <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>101394</v>
+        <v>110040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5154,28 +5203,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224885</v>
+        <v>221184</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -5186,10 +5235,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500037</v>
+        <v>500092</v>
       </c>
       <c r="R39" t="n">
-        <v>7003121</v>
+        <v>7003061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5253,16 +5302,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849905</t>
+          <t>https://artportalen.se/Sighting/135849865</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849906</v>
+        <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>101394</v>
+        <v>110040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5270,28 +5319,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224885</v>
+        <v>221184</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5302,10 +5351,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500014</v>
+        <v>500055</v>
       </c>
       <c r="R40" t="n">
-        <v>7003143</v>
+        <v>7003061</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5368,6 +5417,1631 @@
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849866</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135849888</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98157</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>500042</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849888</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135849890</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>500078</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849890</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135849891</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>499954</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7003071</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849891</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135849999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>500192</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7003171</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849999</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135850000</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>500105</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7003131</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135850001</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>500070</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7003120</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850001</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135850002</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>500005</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7003116</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850002</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135850003</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500039</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7003109</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850003</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135850005</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>499962</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7003092</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850005</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135850006</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>499967</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7003113</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850006</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135849874</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102042</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500036</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7003135</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849874</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135849904</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500029</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7003136</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849904</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135849905</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500037</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7003121</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849905</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849906</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500014</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003143</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135849906</t>
         </is>
@@ -5414,6 +7088,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135849846</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135849847</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135849848</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102042</v>
+        <v>102043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135849846</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135849847</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135849848</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102043</v>
+        <v>102049</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135849846</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135849847</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135849848</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102049</v>
+        <v>102050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111278</v>
+        <v>111289</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102050</v>
+        <v>102061</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135849846</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135849847</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135849848</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111289</v>
+        <v>111302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102061</v>
+        <v>102074</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102074</v>
+        <v>102075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135849879</v>
       </c>
       <c r="B10" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>135849846</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>135849847</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135849848</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135849849</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>135849871</v>
       </c>
       <c r="B15" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135849872</v>
       </c>
       <c r="B16" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135849868</v>
       </c>
       <c r="B17" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102075</v>
+        <v>102088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28079-2026 artfynd.xlsx
+++ b/artfynd/A 28079-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135849960</v>
       </c>
       <c r="B4" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>135849961</v>
       </c>
       <c r="B5" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>135849962</v>
       </c>
       <c r="B6" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>135850021</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>135850022</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>135849908</v>
       </c>
       <c r="B9" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>135849938</v>
       </c>
       <c r="B18" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135849939</v>
       </c>
       <c r="B19" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135849940</v>
       </c>
       <c r="B20" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135849941</v>
       </c>
       <c r="B21" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>135849942</v>
       </c>
       <c r="B22" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>135849943</v>
       </c>
       <c r="B23" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>135849945</v>
       </c>
       <c r="B24" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135849946</v>
       </c>
       <c r="B25" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>135849947</v>
       </c>
       <c r="B26" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849948</v>
       </c>
       <c r="B27" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135850036</v>
       </c>
       <c r="B28" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>135849924</v>
       </c>
       <c r="B29" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135849925</v>
       </c>
       <c r="B30" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135849926</v>
       </c>
       <c r="B31" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>135849927</v>
       </c>
       <c r="B32" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135849928</v>
       </c>
       <c r="B33" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>135849929</v>
       </c>
       <c r="B34" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>135849912</v>
       </c>
       <c r="B35" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>135849986</v>
       </c>
       <c r="B36" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>135849987</v>
       </c>
       <c r="B37" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135849988</v>
       </c>
       <c r="B38" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>135849865</v>
       </c>
       <c r="B39" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135849866</v>
       </c>
       <c r="B40" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>135849888</v>
       </c>
       <c r="B41" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135849890</v>
       </c>
       <c r="B42" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>135849891</v>
       </c>
       <c r="B43" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>135849999</v>
       </c>
       <c r="B44" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135850000</v>
       </c>
       <c r="B45" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135850001</v>
       </c>
       <c r="B46" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>135850002</v>
       </c>
       <c r="B47" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>135850003</v>
       </c>
       <c r="B48" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>135850005</v>
       </c>
       <c r="B49" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>135850006</v>
       </c>
       <c r="B50" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>135849874</v>
       </c>
       <c r="B51" t="n">
-        <v>102088</v>
+        <v>102089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>135849904</v>
       </c>
       <c r="B52" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135849905</v>
       </c>
       <c r="B53" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135849906</v>
       </c>
       <c r="B54" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
